--- a/www/download/IND.abstract_labour.emp.s.mv.rpA1.xlsx
+++ b/www/download/IND.abstract_labour.emp.s.mv.rpA1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15262.516</t>
+          <t>15262515700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15313.314</t>
+          <t>15313313900</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15492.621</t>
+          <t>15492620800</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15809.188</t>
+          <t>15809187500</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>16175.072</t>
+          <t>16175072100</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>16516.061</t>
+          <t>16516060800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16578.653</t>
+          <t>16578652800</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16907.067</t>
+          <t>16907066600</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>17174.77</t>
+          <t>17174769880</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>17645.28</t>
+          <t>17645279900</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>18026.47</t>
+          <t>18026470142.4781</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>18424.644</t>
+          <t>18424644486.6276</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>18919.606</t>
+          <t>18919606150.8565</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>20488.035</t>
+          <t>20488034752.5043</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>21545.023</t>
+          <t>21545022822.5012</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6149.242</t>
+          <t>6149242000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6212.278</t>
+          <t>6212278000</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6288.025</t>
+          <t>6288025000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>6361.278</t>
+          <t>6361278000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6424.814</t>
+          <t>6424814000</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6518.098</t>
+          <t>6518098000</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6559.398</t>
+          <t>6559398000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6542.049</t>
+          <t>6542049000</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>6583.091</t>
+          <t>6583091000</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6630.014</t>
+          <t>6630014000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>6658.907</t>
+          <t>6658907000</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>6717.025</t>
+          <t>6717025000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>6788.639</t>
+          <t>6788639000</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>6968.04</t>
+          <t>6968039603.14124</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>6613.166</t>
+          <t>6613166129.92754</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5537.162</t>
+          <t>5537161563.7762</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5534.511</t>
+          <t>5534510709.31955</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5603.697</t>
+          <t>5603696769.77835</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5685.502</t>
+          <t>5685501816.20563</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5787.52</t>
+          <t>5787519958.512</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5961.599</t>
+          <t>5961599139.40131</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6030.447</t>
+          <t>6030447322.11266</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5990.895</t>
+          <t>5990894959.81838</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>5992.714</t>
+          <t>5992714488.46031</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6057.565</t>
+          <t>6057565469.25483</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>6122.792</t>
+          <t>6122792221.14095</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>6209.157</t>
+          <t>6209157272.36833</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>6331.202</t>
+          <t>6331201978.02203</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>6412.834</t>
+          <t>6412833763.09854</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>6293.109</t>
+          <t>6293109306.44956</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6025.009</t>
+          <t>6025008671.9305</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6178.773</t>
+          <t>6178772891.40574</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5980.411</t>
+          <t>5980411261.78583</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5727.669</t>
+          <t>5727669207.89169</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5532.414</t>
+          <t>5532413588.31211</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5313.109</t>
+          <t>5313109000</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5310.295</t>
+          <t>5310295000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5320.554</t>
+          <t>5320554000</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5442.215</t>
+          <t>5442215000</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5662.196</t>
+          <t>5662196000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>5797.413</t>
+          <t>5797413000</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>5998.505</t>
+          <t>5998505000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>6165.971</t>
+          <t>6165971000</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6241.306</t>
+          <t>6241305983.29216</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>6207.343</t>
+          <t>6207342931.12282</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>157522.872</t>
+          <t>157522871815.931</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>154975.268</t>
+          <t>154975267826.828</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>158449.89</t>
+          <t>158449890428.51</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>158213.64</t>
+          <t>158213639601.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>164642.11</t>
+          <t>164642110208.336</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>170373.593</t>
+          <t>170373593179.634</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>172038.194</t>
+          <t>172038193512.572</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>179030.577</t>
+          <t>179030577348.644</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>181564.871</t>
+          <t>181564871488.186</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>189442.152</t>
+          <t>189442152116.396</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>193103.106</t>
+          <t>193103105662.399</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>197824.902</t>
+          <t>197824901761.945</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>201071.541</t>
+          <t>201071540982.591</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>204334.615</t>
+          <t>204334614712.513</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>205284.27</t>
+          <t>205284270174.38</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24163.261</t>
+          <t>24163261022.4366</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24606.801</t>
+          <t>24606801459.0087</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24972.061</t>
+          <t>24972060998.11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>25524.081</t>
+          <t>25524080998.21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>26167.659</t>
+          <t>26167658998.02</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>26709.975</t>
+          <t>26709974998.01</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>26868.102</t>
+          <t>26868101998.04</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27201.949</t>
+          <t>27201948998.03</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>27611.262</t>
+          <t>27611261998.03</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>28349.86</t>
+          <t>28349859998.03</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>28533.803</t>
+          <t>28533802998.04</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>28986.532</t>
+          <t>28986531998.04</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>29625.12</t>
+          <t>29625119998.04</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>30221.823</t>
+          <t>30221823441.5849</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>28824.294</t>
+          <t>28824294040.15</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1214994.346</t>
+          <t>1214994345987.44</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1229546.798</t>
+          <t>1229546798303.14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1238180.551</t>
+          <t>1238180550922.83</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1236037.648</t>
+          <t>1236037647711.61</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1235342.034</t>
+          <t>1235342034135.8</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1260851.623</t>
+          <t>1260851622508.23</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1339026.837</t>
+          <t>1339026837208.78</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1400107.894</t>
+          <t>1400107894462.17</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1440056.64</t>
+          <t>1440056639637.87</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1470748.352</t>
+          <t>1470748352444.09</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1476522.787</t>
+          <t>1476522786576.37</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1465602.046</t>
+          <t>1465602046028.31</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1492885.254</t>
+          <t>1492885253576.94</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1538102.906</t>
+          <t>1538102906351.87</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1555748.515</t>
+          <t>1555748515000.03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>556.844</t>
+          <t>556844000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>559.558</t>
+          <t>559558000</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>565.864</t>
+          <t>565864000</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>576.508</t>
+          <t>576508000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>590.902</t>
+          <t>590902000</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>605.96</t>
+          <t>605960000</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>626.986</t>
+          <t>626986000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>631.03</t>
+          <t>631030000</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>652.422</t>
+          <t>652422000</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>663.882</t>
+          <t>663882000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>679.879</t>
+          <t>679879000</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>694.745</t>
+          <t>694745000</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>715.064</t>
+          <t>715064000</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>724.744</t>
+          <t>724744333.122296</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>725.571</t>
+          <t>725571484.03977</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10385.389</t>
+          <t>10385389000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10466.783</t>
+          <t>10466783000</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10506.601</t>
+          <t>10506601000</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>10374.742</t>
+          <t>10374742000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10183.985</t>
+          <t>10183985000</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>10157.388</t>
+          <t>10157388000</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>9751.944</t>
+          <t>9751944000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9700.054</t>
+          <t>9700054000</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>9578.514</t>
+          <t>9578514000</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>9651.583</t>
+          <t>9651583000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>9808.906</t>
+          <t>9808906000</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>9974.58</t>
+          <t>9974580000</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>10175.114</t>
+          <t>10175114000</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>10460.522</t>
+          <t>10460522320.2866</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>10103.591</t>
+          <t>10103590571.8892</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>57679.197</t>
+          <t>57679196738.1535</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>56921.734</t>
+          <t>56921734359.5757</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>56526.422</t>
+          <t>56526421658.4249</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>56997.003</t>
+          <t>56997003030.2113</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>57318.04</t>
+          <t>57318039756.847</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>57658.023</t>
+          <t>57658022765.4988</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>57334.344</t>
+          <t>57334343544.1498</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>56510</t>
+          <t>5.651e+10</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>55724</t>
+          <t>5.5724e+10</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>56044</t>
+          <t>5.6044e+10</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>55693</t>
+          <t>5.5693e+10</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>55862</t>
+          <t>5.5862e+10</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>56788</t>
+          <t>5.6788e+10</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>57721.711</t>
+          <t>57721710897.5781</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>56739.567</t>
+          <t>56739567063.1994</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3946.525</t>
+          <t>3946525000</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3968.857</t>
+          <t>3968857000</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4069.596</t>
+          <t>4069596000</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4172.171</t>
+          <t>4172171000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4237.91</t>
+          <t>4237910000</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4300.641</t>
+          <t>4300641000</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4354.175</t>
+          <t>4354175000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4335.214</t>
+          <t>4335214000</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4278.018</t>
+          <t>4278018000</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>4260.686</t>
+          <t>4260686000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>4305.218</t>
+          <t>4305218000</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4413.431</t>
+          <t>4413431000</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>4490.221</t>
+          <t>4490221000</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>4563.611</t>
+          <t>4563611344.86316</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>4426.213</t>
+          <t>4426213429.23584</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>23514.494</t>
+          <t>23514493699.9123</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>23846.269</t>
+          <t>23846269000.3119</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>24704.464</t>
+          <t>24704463700.2885</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25856.859</t>
+          <t>25856858599.9331</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>27049.908</t>
+          <t>27049908499.8955</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>28401.149</t>
+          <t>28401148900</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>29231.75</t>
+          <t>29231750000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>29836.085</t>
+          <t>29836085000</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>30494.884</t>
+          <t>30494883600</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>31273.815</t>
+          <t>31273815100</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>32133.3</t>
+          <t>32133300400</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>33146.634</t>
+          <t>33146633700</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>33757.146</t>
+          <t>33757145700</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>33692.434</t>
+          <t>33692434300.156</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>31673.494</t>
+          <t>31673493566.3532</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1229.997</t>
+          <t>1229996614.94619</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1202.232</t>
+          <t>1202231511.84761</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1197.109</t>
+          <t>1197108626.34275</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1175.736</t>
+          <t>1175735691.08207</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1121.586</t>
+          <t>1121585837.85306</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1108.908</t>
+          <t>1108907704</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1114.127</t>
+          <t>1114127481.65549</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1127.774</t>
+          <t>1127773589</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1148.49</t>
+          <t>1148490171</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1152.113</t>
+          <t>1152113319.26823</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1185.772</t>
+          <t>1185772206</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1259.874</t>
+          <t>1259874378</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1271.582</t>
+          <t>1271582452.36758</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1270.92</t>
+          <t>1270919798.47214</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1097.816</t>
+          <t>1097815928.62376</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3645.8</t>
+          <t>3645800000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3695.2</t>
+          <t>3695200000</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3811.8</t>
+          <t>3811800000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3860.6</t>
+          <t>3860600000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3964.7</t>
+          <t>3964700000</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4014.9</t>
+          <t>4014900000</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4027.8</t>
+          <t>4027800000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4049.8</t>
+          <t>4049800000</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4034.9</t>
+          <t>4034900000</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>4061.5</t>
+          <t>4061500000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>4099.4</t>
+          <t>4099400000</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>4157.8</t>
+          <t>4157800000</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>4242.2</t>
+          <t>4242200000</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>4292.752</t>
+          <t>4292752281.33335</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4119.799</t>
+          <t>4119798894.31217</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>35398.487</t>
+          <t>35398486633.4996</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>35593.522</t>
+          <t>35593522062.4628</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35567.12</t>
+          <t>35567119821.5873</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>35886.025</t>
+          <t>35886025437.3558</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>36560.307</t>
+          <t>36560307098.763</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>36624.674</t>
+          <t>36624673723.8078</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>37045.329</t>
+          <t>37045328742.0656</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>36392.365</t>
+          <t>36392364963.501</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>36304.468</t>
+          <t>36304467884.9718</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>36998.921</t>
+          <t>36998920660.15</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>37190.257</t>
+          <t>37190256522.7356</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>37129.413</t>
+          <t>37129413142.017</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>38094.743</t>
+          <t>38094742835.7833</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>38629.06</t>
+          <t>38629060336.6229</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>37490.919</t>
+          <t>37490919447.5879</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>44993.802</t>
+          <t>44993802000</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45389.552</t>
+          <t>45389552000</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>46176.543</t>
+          <t>46176543000</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>46487.59</t>
+          <t>46487590000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>46808.741</t>
+          <t>46808741000</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>47050.896</t>
+          <t>47050896000</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>47522.65</t>
+          <t>47522650000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>47355.712</t>
+          <t>47355712000</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>47271.276</t>
+          <t>47271276000</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>47631.936</t>
+          <t>47631936000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>48233.604</t>
+          <t>48233604000</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>48510.801</t>
+          <t>48510801000</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>48898.444</t>
+          <t>48898444000</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>48638.184</t>
+          <t>48638184000</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>47697.788</t>
+          <t>47697788000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>8769.443</t>
+          <t>8769442990</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8633.201</t>
+          <t>8633201448</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>8451.014</t>
+          <t>8451013902</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>8788.894</t>
+          <t>8788894157</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>8982.557</t>
+          <t>8982557105</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>9024.035</t>
+          <t>9024035231</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>9037.172</t>
+          <t>9037172446</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>9187.541</t>
+          <t>9187540591</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>9268.693</t>
+          <t>9268692553</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>9400.019</t>
+          <t>9400019109</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>9491.005</t>
+          <t>9491004683</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>10097.279</t>
+          <t>10097278528</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>10117.274</t>
+          <t>10117273801</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>10032.667</t>
+          <t>10032667395.8805</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>10458.883</t>
+          <t>10458882644.303</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>8079.711</t>
+          <t>8079711219.40055</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8069.551</t>
+          <t>8069551307.42483</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>8160.662</t>
+          <t>8160661798.29138</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>8290.864</t>
+          <t>8290864349.17157</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8587.375</t>
+          <t>8587374640.12717</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8673.529</t>
+          <t>8673528917</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8452.565</t>
+          <t>8452564657</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8474.813</t>
+          <t>8474813414</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8369.327</t>
+          <t>8369326785</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8304.772</t>
+          <t>8304771954</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>8284.195</t>
+          <t>8284194674</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8317.391</t>
+          <t>8317391408</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>8277.404</t>
+          <t>8277404373</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>8076.164</t>
+          <t>8076163693.74774</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>7854.807</t>
+          <t>7854806818.35529</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>126800.04</t>
+          <t>126800040199.903</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>130791.792</t>
+          <t>130791791531.132</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>130793.751</t>
+          <t>130793750834.673</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>135652.383</t>
+          <t>135652382970.267</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>151359.325</t>
+          <t>151359324800.349</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>150969.555</t>
+          <t>150969554560.976</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>152843.242</t>
+          <t>152843242257.524</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>160887.359</t>
+          <t>160887359160.359</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>164503.981</t>
+          <t>164503980589.901</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>171431.406</t>
+          <t>171431405963.774</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>147126.681</t>
+          <t>147126680531.104</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>138944.74</t>
+          <t>138944740444.118</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>142588.35</t>
+          <t>142588349836.274</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>146166.663</t>
+          <t>146166663137.177</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>149772.086</t>
+          <t>149772086036.291</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>883269.411</t>
+          <t>883269411041.813</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>912034.175</t>
+          <t>912034175416.31</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>921899.495</t>
+          <t>921899495067.775</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>929558.011</t>
+          <t>929558010777.49</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>921995.643</t>
+          <t>921995642624.479</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>963502.007</t>
+          <t>963502007286.061</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1001482.189</t>
+          <t>1001482188929.38</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>985730.519</t>
+          <t>985730519159.591</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1045978.848</t>
+          <t>1045978847742.94</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1068687.044</t>
+          <t>1068687043754.34</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1098153.176</t>
+          <t>1098153176017.84</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1102781.829</t>
+          <t>1102781829254.43</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1077429.619</t>
+          <t>1077429618585.69</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1085691.063</t>
+          <t>1085691063414.01</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1092178.443</t>
+          <t>1092178442629.47</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2547.899</t>
+          <t>2547899286.28545</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2653.568</t>
+          <t>2653568154.19399</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2769.255</t>
+          <t>2769255347.01174</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2978.043</t>
+          <t>2978042757.53249</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3146.232</t>
+          <t>3146232450.2526</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3278.661</t>
+          <t>3278660739.29116</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3360.912</t>
+          <t>3360911560.89258</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3387.924</t>
+          <t>3387924434.28586</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>3426.525</t>
+          <t>3426524671.01494</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>3525.15</t>
+          <t>3525150168.57143</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>3696.057</t>
+          <t>3696056554.17269</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>3837.868</t>
+          <t>3837868146.12786</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>3943.674</t>
+          <t>3943673918.4152</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>3993.21</t>
+          <t>3993210073.6081</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>3609.214</t>
+          <t>3609213724.27385</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>40599.839</t>
+          <t>40599839200</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>41143.486</t>
+          <t>41143485600</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>41054.172</t>
+          <t>41054172200</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>41827.744</t>
+          <t>41827743700</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>42189.165</t>
+          <t>42189165000</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>42680.822</t>
+          <t>42680822000</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>43115.103</t>
+          <t>43115102911.5583</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>43564.346</t>
+          <t>43564346300</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>44087.232</t>
+          <t>44087231700</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>44292.887</t>
+          <t>44292887500</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>44369.551</t>
+          <t>44369551000</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>45142.592</t>
+          <t>45142592300</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>45750.837</t>
+          <t>45750836700</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>45573.368</t>
+          <t>45573368085.9512</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>44374.474</t>
+          <t>44374474453.1903</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>128222.472</t>
+          <t>128222471703.372</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>128765.062</t>
+          <t>128765062457.942</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>127817.187</t>
+          <t>127817186581.938</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>124807.729</t>
+          <t>124807729306.285</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>121678.753</t>
+          <t>121678752876.065</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>121538.02</t>
+          <t>121538020243.119</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>120328.064</t>
+          <t>120328063648.719</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>117808.29</t>
+          <t>117808290223.311</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>117674.143</t>
+          <t>117674143014.12</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>117553.502</t>
+          <t>117553502189.724</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>115915.217</t>
+          <t>115915216876.385</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>117204.754</t>
+          <t>117204754014.252</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>117623.105</t>
+          <t>117623105374.446</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>114963.431</t>
+          <t>114963431160.589</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>105856.42</t>
+          <t>105856420383.388</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>51162.193</t>
+          <t>51162193207.3174</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50854.307</t>
+          <t>50854306766.5198</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>51302.684</t>
+          <t>51302683701.8651</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>48438.841</t>
+          <t>48438840955.0654</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>50338.267</t>
+          <t>50338267495.631</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>51635.805</t>
+          <t>51635804554.3794</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>52111.252</t>
+          <t>52111252339.1222</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>53200.369</t>
+          <t>53200369020.8505</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>53124.252</t>
+          <t>53124251939.0588</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>55887.331</t>
+          <t>55887330835.7667</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>54220.887</t>
+          <t>54220886780.1216</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>54641.266</t>
+          <t>54641265800.5858</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>53454.996</t>
+          <t>53454995526.7301</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>53781.163</t>
+          <t>53781163147.4982</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>53619.22</t>
+          <t>53619219783.3406</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2571.545</t>
+          <t>2571545000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2595.514</t>
+          <t>2595513640.41746</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2602.912</t>
+          <t>2602912000</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2659.424</t>
+          <t>2659424000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2522.551</t>
+          <t>2522551000</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2583.224</t>
+          <t>2583224000</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2464.605</t>
+          <t>2464604694.9485</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2513.641</t>
+          <t>2513640732.24568</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2546.154</t>
+          <t>2546154000</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2578.763</t>
+          <t>2578763000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2732.644</t>
+          <t>2732644442.90056</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2760.572</t>
+          <t>2760571519.06275</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2868.389</t>
+          <t>2868389000</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2915.074</t>
+          <t>2915073729.0729</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2692.609</t>
+          <t>2692608724.27263</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>347.657</t>
+          <t>347656915.269726</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>356.525</t>
+          <t>356524995.788177</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>369.458</t>
+          <t>369457631.879648</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>384.402</t>
+          <t>384402303.337503</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>405.671</t>
+          <t>405671073.680577</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>430.518</t>
+          <t>430517951.58852</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>450.569</t>
+          <t>450568815.623625</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>464.123</t>
+          <t>464122820.701766</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>472.77</t>
+          <t>472770403.81916</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>488.325</t>
+          <t>488325290.497368</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>502.605</t>
+          <t>502605032.235121</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>520.128</t>
+          <t>520128357.329005</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>542.963</t>
+          <t>542962614.873351</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>608.296</t>
+          <t>608295667.828685</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>598.729</t>
+          <t>598728643.090978</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1514.59</t>
+          <t>1514590032.04503</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1493.457</t>
+          <t>1493457060.44326</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1534.138</t>
+          <t>1534138017.54915</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1582.666</t>
+          <t>1582666354.38879</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>1567999923.67959</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1526.578</t>
+          <t>1526577820.99134</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1501.692</t>
+          <t>1501692005.47824</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1489.298</t>
+          <t>1489298335.19792</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1523.524</t>
+          <t>1523523547.78141</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1544.045</t>
+          <t>1544044635.48969</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1592.962</t>
+          <t>1592961685.28713</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1664.197</t>
+          <t>1664196888.97509</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1737.5</t>
+          <t>1737499758.92836</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1686.662</t>
+          <t>1686661984.74619</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1417.767</t>
+          <t>1417766576.16466</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>72200.833</t>
+          <t>72200832997.9626</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>74795.877</t>
+          <t>74795877051.8443</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>76346.732</t>
+          <t>76346732485.9179</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>78831.744</t>
+          <t>78831744217.3891</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>82030.457</t>
+          <t>82030457245.5939</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>84949.798</t>
+          <t>84949797530.0829</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>86514.939</t>
+          <t>86514939453.1646</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>88013.122</t>
+          <t>88013122035.8712</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>90547.766</t>
+          <t>90547765814.5052</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>94579.114</t>
+          <t>94579114105.3758</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>95650.793</t>
+          <t>95650792682.7358</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>98012.058</t>
+          <t>98012058037.8815</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>99244.457</t>
+          <t>99244457230.2164</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>106428.421</t>
+          <t>106428420670.098</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>104819.379</t>
+          <t>104819379402.596</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>272.138</t>
+          <t>272137948.345955</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>273.341</t>
+          <t>273340778.991406</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>274.43</t>
+          <t>274430285.096707</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>278.239</t>
+          <t>278238586.090692</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>282.002</t>
+          <t>282002153.713565</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>285.185</t>
+          <t>285185181.586899</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>244.532</t>
+          <t>244531553.853267</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>288.899</t>
+          <t>288899268.348295</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>277.161</t>
+          <t>277160855.202434</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>284000169.133413</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>286.041</t>
+          <t>286041214.56216</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>287.987</t>
+          <t>287986878.933645</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>300.123</t>
+          <t>300122877.824299</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>306.883</t>
+          <t>306882575.853023</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>307.78</t>
+          <t>307779660.295915</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>10445.244</t>
+          <t>10445244203.6327</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10702.777</t>
+          <t>10702776704.0685</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10961.388</t>
+          <t>10961388159.0455</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>11146.709</t>
+          <t>11146708726.7442</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>11403.058</t>
+          <t>11403058040.3236</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>11641.135</t>
+          <t>11641134545.9245</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>11791.079</t>
+          <t>11791078936</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>11723.033</t>
+          <t>11723033019</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>11603.664</t>
+          <t>11603663726</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>11489.169</t>
+          <t>11489168633</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>11496.405</t>
+          <t>11496405247</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>11679.322</t>
+          <t>11679322035</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>11950.122</t>
+          <t>11950121943</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>12164.649</t>
+          <t>12164648567.3088</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>12042.709</t>
+          <t>12042709012.2354</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>28305.086</t>
+          <t>28305086293.1525</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>28879.294</t>
+          <t>28879294419.0028</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>29662.441</t>
+          <t>29662440618.8973</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>30129.465</t>
+          <t>30129464561.2833</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>29829.818</t>
+          <t>29829817522.3089</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>28892.502</t>
+          <t>28892502127.8591</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>26456.571</t>
+          <t>26456570789.3266</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>25507.399</t>
+          <t>25507398965.6909</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>25162.379</t>
+          <t>25162379461.1629</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>25538.377</t>
+          <t>25538377300.9695</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>25769.666</t>
+          <t>25769666149.1946</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>26509.432</t>
+          <t>26509432484.7037</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>27585.81</t>
+          <t>27585810137.3996</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>28604.274</t>
+          <t>28604273526.7837</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>28297.15</t>
+          <t>28297149673.6112</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>8693.292</t>
+          <t>8693291604.54445</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8720.653</t>
+          <t>8720653411.22951</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>8753.428</t>
+          <t>8753428328.46158</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>8907.131</t>
+          <t>8907131147.44126</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>9115.373</t>
+          <t>9115372875.80184</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>9296.705</t>
+          <t>9296704880.21882</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>9445.794</t>
+          <t>9445793656.45739</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>9496.836</t>
+          <t>9496836440.10518</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>9343.179</t>
+          <t>9343179090.48792</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>9429.324</t>
+          <t>9429324368.61149</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>9396.913</t>
+          <t>9396912528.61733</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>9539.606</t>
+          <t>9539605679.76632</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>9588.836</t>
+          <t>9588835861.71984</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>9552.777</t>
+          <t>9552776868.75569</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>9196.084</t>
+          <t>9196083608.80906</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>17008.077</t>
+          <t>17008076566.2517</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>17598.162</t>
+          <t>17598162191.4035</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>16800.278</t>
+          <t>16800278404.2581</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>16391.695</t>
+          <t>16391695466.7451</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20083.159</t>
+          <t>20083159000</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>19959.764</t>
+          <t>19959764000</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19742.438</t>
+          <t>19742438000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>17876.156</t>
+          <t>17876156000</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>17579.559</t>
+          <t>17579559000</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>17371.251</t>
+          <t>17371251000</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>17171.308</t>
+          <t>17171308000</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>17305.201</t>
+          <t>17305201000</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>17588.497</t>
+          <t>17588497000</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>17593.169</t>
+          <t>17593169000</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>17338.698</t>
+          <t>17338697861.6088</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>147480.245</t>
+          <t>147480245205.283</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>145736.147</t>
+          <t>145736147183.706</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>143947.993</t>
+          <t>143947992992.623</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>139814.023</t>
+          <t>139814022951.23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>140635.672</t>
+          <t>140635671978.995</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>142066.304</t>
+          <t>142066304119.395</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>143725.423</t>
+          <t>143725423376.037</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>144652.032</t>
+          <t>144652032453.852</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>145979.323</t>
+          <t>145979322680.39</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>147237.004</t>
+          <t>147237003746.657</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>147629.163</t>
+          <t>147629163489.76</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>148512.153</t>
+          <t>148512152853.828</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>150394.471</t>
+          <t>150394470761.21</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>151060.45</t>
+          <t>151060450175.413</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>147091.434</t>
+          <t>147091434048</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3956.528</t>
+          <t>3956528000</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3962.421</t>
+          <t>3962421000</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3915.031</t>
+          <t>3915031000</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>3833.549</t>
+          <t>3833549000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3735.161</t>
+          <t>3735161000</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3675.511</t>
+          <t>3675511000</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3644.524</t>
+          <t>3644524000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>3539.907</t>
+          <t>3539907000</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>3463.997</t>
+          <t>3463997000</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>3555.952</t>
+          <t>3555952000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>3679.17</t>
+          <t>3679170000</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>3728.418</t>
+          <t>3728418000</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>3883.844</t>
+          <t>3883844000</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>4039.07</t>
+          <t>4039070106.46838</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>3988.091</t>
+          <t>3988090533.37074</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1708.758</t>
+          <t>1708757625.80647</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1670.15</t>
+          <t>1670150120.2685</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1638.628</t>
+          <t>1638627648.55927</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1629.509</t>
+          <t>1629509098.6178</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1644.428</t>
+          <t>1644428387.08447</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1660.151</t>
+          <t>1660151050.6775</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1662.069</t>
+          <t>1662068675.97344</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1682.333</t>
+          <t>1682333193.89346</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1671.121</t>
+          <t>1671120525.92652</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1671.611</t>
+          <t>1671610829.04208</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1664.697</t>
+          <t>1664696902.32574</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1689.328</t>
+          <t>1689328102.08285</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1740.358</t>
+          <t>1740358030.68536</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1819.538</t>
+          <t>1819537674.08294</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1778.476</t>
+          <t>1778476269.73853</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>6772.82</t>
+          <t>6772819999.99282</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6770.69</t>
+          <t>6770689999.99285</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6703.5</t>
+          <t>6703500000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>6809.79</t>
+          <t>6809790000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6988.38</t>
+          <t>6988380000.0107</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>7061.95</t>
+          <t>7061950000.00911</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>7105.7</t>
+          <t>7105700000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>7006.6</t>
+          <t>7006600000.00862</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>6908.1</t>
+          <t>6908100000</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>6963.43</t>
+          <t>6963430000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>6979.96</t>
+          <t>6979960000</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>7.072e+09</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>7319.33</t>
+          <t>7319330000</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>7362.323</t>
+          <t>7362323182.22011</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>7146.911</t>
+          <t>7146911162.50548</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>42695.615</t>
+          <t>42695615300.7843</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>44294.708</t>
+          <t>44294708495.0847</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>44759.107</t>
+          <t>44759106572.0011</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>43374.73</t>
+          <t>43374729508.1917</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>43618.102</t>
+          <t>43618102103.68</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>42290.063</t>
+          <t>42290062724</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>42188.186</t>
+          <t>42188185937.76</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>41613.735</t>
+          <t>41613735196.92</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>41088.621</t>
+          <t>41088621000</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>41681.976</t>
+          <t>41681976000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>42517.307</t>
+          <t>42517307455.04</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>41001.067</t>
+          <t>41001067162.3316</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>39622.583</t>
+          <t>39622583151.2949</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>40258.093</t>
+          <t>40258093077.2749</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>40019.218</t>
+          <t>40019217908</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>21651.582</t>
+          <t>21651582189.6789</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>21306.613</t>
+          <t>21306613261.9126</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>21621.853</t>
+          <t>21621852706.019</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>21389.203</t>
+          <t>21389202863.1726</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>21466.651</t>
+          <t>21466650718.1514</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>21802.7</t>
+          <t>21802699817.3186</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>20446.521</t>
+          <t>20446520684.4522</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>20645.819</t>
+          <t>20645819397.8129</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>20895.479</t>
+          <t>20895478594.8239</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>21547.134</t>
+          <t>21547134118.0846</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>21808.029</t>
+          <t>21808029300.3046</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>22052.318</t>
+          <t>22052317653.749</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>22426.051</t>
+          <t>22426050893.6546</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>22584.97</t>
+          <t>22584970372.8856</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>21729.434</t>
+          <t>21729434381.5685</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>242776.093</t>
+          <t>242776092779.119</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>246938.593</t>
+          <t>246938593291.553</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>253228.389</t>
+          <t>253228388684.215</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>258805.731</t>
+          <t>258805730809.544</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>263627.014</t>
+          <t>263627013743.852</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>269026.187</t>
+          <t>269026187370.179</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>266094.82</t>
+          <t>266094819734.222</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>262808.915</t>
+          <t>262808915243.401</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>261841.126</t>
+          <t>261841125587.143</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>264757.46</t>
+          <t>264757460055.455</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>267643.044</t>
+          <t>267643044069.724</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>273342.068</t>
+          <t>273342067665.799</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>275293.945</t>
+          <t>275293944514.337</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>271688.068</t>
+          <t>271688067727.256</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>259200.648</t>
+          <t>259200647761.736</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1581950.09</t>
+          <t>1581950090380.27</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1632216.323</t>
+          <t>1632216323446.71</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1661461.975</t>
+          <t>1661461975045.46</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1675206.949</t>
+          <t>1675206949481.46</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1699153.059</t>
+          <t>1699153059439.56</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1763177.932</t>
+          <t>1763177932464.47</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1837303.246</t>
+          <t>1837303245908.48</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1878897.895</t>
+          <t>1878897894530.26</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1972073.419</t>
+          <t>1972073419433.81</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2057200.705</t>
+          <t>2057200705221.21</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2101215.075</t>
+          <t>2101215074715.22</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2166673.727</t>
+          <t>2166673727183.3</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2217052.892</t>
+          <t>2217052892146.03</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2300250.74</t>
+          <t>2300250740267.96</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2339590.627</t>
+          <t>2339590626746.61</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5050806.142</t>
+          <t>5050806142338.25</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5155267.84</t>
+          <t>5155267839757.84</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5214922.674</t>
+          <t>5214922674001.2</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>5240263.707</t>
+          <t>5240263706642.2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>5294293.575</t>
+          <t>5294293575380.68</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>5443795.236</t>
+          <t>5443795235834.71</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5634934.236</t>
+          <t>5634934235581.34</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>5731499.926</t>
+          <t>5731499925857.87</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>5933322.875</t>
+          <t>5933322874864.6</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>6103273.608</t>
+          <t>6103273607955.89</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>6167087.164</t>
+          <t>6167087163760.7</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>6238229.391</t>
+          <t>6238229391165.57</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>6308545.275</t>
+          <t>6308545274711.33</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>6459964.684</t>
+          <t>6459964683502.91</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>6489569.767</t>
+          <t>6489569767236.63</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>abstract_labour.emp.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
